--- a/tabtools/demo/demo_regtab_models.xlsx
+++ b/tabtools/demo/demo_regtab_models.xlsx
@@ -646,7 +646,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -656,22 +656,17 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <b/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+      <sz val="12"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -683,7 +678,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -693,313 +688,213 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <left/>
       <right style="thin"/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1021,274 +916,274 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="40" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="10" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="10" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="40" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="40" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="D10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="42" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="51" t="s">
+      <c r="D12" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="40" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="50" t="s">
+      <c r="D13" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="40" t="s">
+      <c r="A14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="50" t="s">
+      <c r="D14" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="A15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="50" t="s">
+      <c r="D15" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="41" t="s">
+      <c r="A16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="52" t="s">
+      <c r="D16" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1318,172 +1213,172 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="A2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="42" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="32" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="32" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="D6" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="51" t="s">
+      <c r="D6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="36" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="40" t="s">
+      <c r="A7" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="D7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="50" t="s">
+      <c r="D7" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="32" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="A8" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="D8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="50" t="s">
+      <c r="D8" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="32" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="40" t="s">
+      <c r="A9" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="D9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="50" t="s">
+      <c r="D9" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="32" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="41" t="s">
+      <c r="A10" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="52" t="s">
+      <c r="D10" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="34" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1513,223 +1408,223 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="10" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="10" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="40" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="10" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="10" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="40" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="51" t="s">
+      <c r="D10" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="50" t="s">
+      <c r="D11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="40" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="50" t="s">
+      <c r="D12" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="41" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="52" t="s">
+      <c r="D13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1758,223 +1653,223 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="40" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="51" t="s">
+      <c r="D9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="40" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="50" t="s">
+      <c r="D10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="50" t="s">
+      <c r="D11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="40" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="50" t="s">
+      <c r="D12" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="41" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="52" t="s">
+      <c r="D13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2004,240 +1899,240 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="40" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="40" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="51" t="s">
+      <c r="D10" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="50" t="s">
+      <c r="D11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="40" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="50" t="s">
+      <c r="D12" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="40" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="50" t="s">
+      <c r="D13" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="41" t="s">
+      <c r="A14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="52" t="s">
+      <c r="D14" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2267,206 +2162,206 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="10" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="40" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="51" t="s">
+      <c r="D9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="40" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="50" t="s">
+      <c r="D10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="50" t="s">
+      <c r="D11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="41" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="52" t="s">
+      <c r="D12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2495,189 +2390,189 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="10" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="40" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="51" t="s">
+      <c r="D9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="40" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="50" t="s">
+      <c r="D10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="41" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="52" t="s">
+      <c r="D11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2705,138 +2600,138 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="51" t="s">
+      <c r="D7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="41" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D8" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="52" t="s">
+      <c r="D8" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2863,189 +2758,189 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="10" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="10" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="10" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="40" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="10" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="10" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="40" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="51" t="s">
+      <c r="D10" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="41" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="52" t="s">
+      <c r="D11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3075,314 +2970,314 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="24" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="G2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="25" t="s">
+      <c r="G2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="20" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="G4" s="47" t="s">
+      <c r="G4" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="H4" s="10" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="47" t="s">
+      <c r="F5" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="H5" s="50" t="s">
+      <c r="H5" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="H6" s="50" t="s">
+      <c r="H6" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="40" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H7" s="50" t="s">
+      <c r="H7" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="G8" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="H8" s="50" t="s">
+      <c r="H8" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="D9" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="46" t="s">
+      <c r="D9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="G9" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="51" t="s">
+      <c r="G9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="40" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="17" t="s">
+      <c r="D10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="G10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="50" t="s">
+      <c r="G10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="17" t="s">
+      <c r="D11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="G11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="50" t="s">
+      <c r="G11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="41" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="D12" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="49" t="s">
+      <c r="D12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="G12" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="52" t="s">
+      <c r="G12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/demo_regtab_models.xlsx
+++ b/tabtools/demo/demo_regtab_models.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="636" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="636" uniqueCount="202">
   <si>
     <t>Table 5h. Multinomial Logit -- Education Level</t>
   </si>
@@ -189,7 +189,7 @@
     <t>Coef.</t>
   </si>
   <si>
-    <t>-0.10</t>
+    <t>0.04</t>
   </si>
   <si>
     <t>0.00</t>
@@ -198,409 +198,397 @@
     <t>-0.01</t>
   </si>
   <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>6.22</t>
+  </si>
+  <si>
+    <t>96131.27</t>
+  </si>
+  <si>
+    <t>96176.97</t>
+  </si>
+  <si>
+    <t>(-0.20, 0.28)</t>
+  </si>
+  <si>
+    <t>(-0.01, 0.00)</t>
+  </si>
+  <si>
+    <t>(-0.20, 0.19)</t>
+  </si>
+  <si>
+    <t>(-0.09, 0.33)</t>
+  </si>
+  <si>
+    <t>(-0.11, 0.31)</t>
+  </si>
+  <si>
+    <t>(5.76, 6.69)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>&lt;0.001</t>
+  </si>
+  <si>
+    <t>Table 5j. Probit Regression -- Cardiovascular Event</t>
+  </si>
+  <si>
+    <t>Probit</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>19417.26</t>
+  </si>
+  <si>
+    <t>19462.95</t>
+  </si>
+  <si>
+    <t>-9702.63</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>(-0.02, 0.08)</t>
+  </si>
+  <si>
+    <t>(-0.00, 0.00)</t>
+  </si>
+  <si>
+    <t>(-0.04, 0.05)</t>
+  </si>
+  <si>
+    <t>(0.01, 0.10)</t>
+  </si>
+  <si>
+    <t>(-0.05, 0.04)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>0.017</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>Table 5k. Ordered Logit -- Education Level</t>
+  </si>
+  <si>
+    <t>Primary to Secondary</t>
+  </si>
+  <si>
+    <t>Secondary to Tertiary</t>
+  </si>
+  <si>
+    <t>Ordered logit</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>-1.07</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>32526.73</t>
+  </si>
+  <si>
+    <t>32572.43</t>
+  </si>
+  <si>
+    <t>-16257.37</t>
+  </si>
+  <si>
+    <t>(0.94, 1.07)</t>
+  </si>
+  <si>
+    <t>(0.96, 1.08)</t>
+  </si>
+  <si>
+    <t>(0.94, 1.06)</t>
+  </si>
+  <si>
+    <t>(-1.22, -0.93)</t>
+  </si>
+  <si>
+    <t>(0.46, 0.75)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Table 5l. Negative Binomial Regression -- Prior Hospitalizations</t>
+  </si>
+  <si>
+    <t>Negative binomial</t>
+  </si>
+  <si>
+    <t>IRR</t>
+  </si>
+  <si>
+    <t>49369.65</t>
+  </si>
+  <si>
+    <t>49422.96</t>
+  </si>
+  <si>
+    <t>-24677.83</t>
+  </si>
+  <si>
+    <t>(0.99, 1.05)</t>
+  </si>
+  <si>
+    <t>(0.98, 1.03)</t>
+  </si>
+  <si>
+    <t>(0.97, 1.02)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Table 5m. GLM Poisson -- Prior Hospitalizations</t>
+  </si>
+  <si>
+    <t>GLM Poisson</t>
+  </si>
+  <si>
+    <t>49367.65</t>
+  </si>
+  <si>
+    <t>49413.35</t>
+  </si>
+  <si>
+    <t>Table 5n. Panel Random-Effects Regression</t>
+  </si>
+  <si>
+    <t>Treatment exposure</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Groups</t>
+  </si>
+  <si>
+    <t>Panel RE</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>2.30</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>(0.32, 0.50)</t>
+  </si>
+  <si>
+    <t>(0.01, 0.03)</t>
+  </si>
+  <si>
+    <t>(1.70, 2.90)</t>
+  </si>
+  <si>
+    <t>Table 5o. Median Regression -- C-Reactive Protein</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>4.47</t>
+  </si>
+  <si>
+    <t>(-0.08, 0.26)</t>
+  </si>
+  <si>
+    <t>(-0.13, 0.14)</t>
+  </si>
+  <si>
+    <t>(-0.03, 0.26)</t>
+  </si>
+  <si>
+    <t>(-0.11, 0.18)</t>
+  </si>
+  <si>
+    <t>(4.15, 4.80)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
     <t>0.13</t>
   </si>
   <si>
-    <t>0.12</t>
-  </si>
-  <si>
-    <t>6.25</t>
-  </si>
-  <si>
-    <t>96130.45</t>
-  </si>
-  <si>
-    <t>96176.15</t>
-  </si>
-  <si>
-    <t>(-0.29, 0.10)</t>
-  </si>
-  <si>
-    <t>(-0.01, 0.00)</t>
-  </si>
-  <si>
-    <t>(-0.21, 0.18)</t>
-  </si>
-  <si>
-    <t>(-0.06, 0.32)</t>
-  </si>
-  <si>
-    <t>(-0.07, 0.31)</t>
-  </si>
-  <si>
-    <t>(5.78, 6.71)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>0.18</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>&lt;0.001</t>
-  </si>
-  <si>
-    <t>Table 5j. Probit Regression -- Cardiovascular Event</t>
-  </si>
-  <si>
-    <t>Probit</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>0.07</t>
-  </si>
-  <si>
-    <t>0.01</t>
-  </si>
-  <si>
-    <t>19417.78</t>
-  </si>
-  <si>
-    <t>19463.47</t>
-  </si>
-  <si>
-    <t>-9702.89</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>(-0.02, 0.06)</t>
-  </si>
-  <si>
-    <t>(0.00, 0.00)</t>
-  </si>
-  <si>
-    <t>(-0.04, 0.05)</t>
-  </si>
-  <si>
-    <t>(0.03, 0.11)</t>
-  </si>
-  <si>
-    <t>(-0.03, 0.05)</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>0.83</t>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Table 5p. Zero-Inflated Count Models</t>
+  </si>
+  <si>
+    <t>Event count: Treatment</t>
+  </si>
+  <si>
+    <t>Event count: Age z-score</t>
+  </si>
+  <si>
+    <t>Event count: Female</t>
+  </si>
+  <si>
+    <t>Inflation equation: Female</t>
+  </si>
+  <si>
+    <t>Inflation equation: Structural-zero risk</t>
+  </si>
+  <si>
+    <t>ZIP</t>
+  </si>
+  <si>
+    <t>-0.15</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>1,500</t>
+  </si>
+  <si>
+    <t>4338.98</t>
+  </si>
+  <si>
+    <t>4376.17</t>
+  </si>
+  <si>
+    <t>-2162.49</t>
+  </si>
+  <si>
+    <t>(-0.26, -0.05)</t>
+  </si>
+  <si>
+    <t>(0.34, 0.44)</t>
+  </si>
+  <si>
+    <t>(0.19, 0.41)</t>
+  </si>
+  <si>
+    <t>(0.15, 0.84)</t>
+  </si>
+  <si>
+    <t>(0.66, 1.04)</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>ZINB</t>
+  </si>
+  <si>
+    <t>-0.14</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>1.07</t>
+  </si>
+  <si>
+    <t>4307.53</t>
+  </si>
+  <si>
+    <t>4350.04</t>
+  </si>
+  <si>
+    <t>-2145.76</t>
+  </si>
+  <si>
+    <t>(-0.26, -0.03)</t>
+  </si>
+  <si>
+    <t>(0.33, 0.45)</t>
+  </si>
+  <si>
+    <t>(0.19, 0.45)</t>
+  </si>
+  <si>
+    <t>(0.26, 1.19)</t>
+  </si>
+  <si>
+    <t>(0.79, 1.35)</t>
+  </si>
+  <si>
+    <t>0.016</t>
   </si>
   <si>
     <t>0.002</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>Table 5k. Ordered Logit -- Education Level</t>
-  </si>
-  <si>
-    <t>Primary to Secondary</t>
-  </si>
-  <si>
-    <t>Secondary to Tertiary</t>
-  </si>
-  <si>
-    <t>Ordered logit</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>-1.07</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>32526.73</t>
-  </si>
-  <si>
-    <t>32572.43</t>
-  </si>
-  <si>
-    <t>-16257.37</t>
-  </si>
-  <si>
-    <t>(0.94, 1.07)</t>
-  </si>
-  <si>
-    <t>(0.96, 1.08)</t>
-  </si>
-  <si>
-    <t>(0.94, 1.06)</t>
-  </si>
-  <si>
-    <t>(-1.22, -0.93)</t>
-  </si>
-  <si>
-    <t>(0.46, 0.75)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Table 5l. Negative Binomial Regression -- Prior Hospitalizations</t>
-  </si>
-  <si>
-    <t>Negative binomial</t>
-  </si>
-  <si>
-    <t>IRR</t>
-  </si>
-  <si>
-    <t>49371.13</t>
-  </si>
-  <si>
-    <t>49424.44</t>
-  </si>
-  <si>
-    <t>-24678.57</t>
-  </si>
-  <si>
-    <t>(0.98, 1.02)</t>
-  </si>
-  <si>
-    <t>(0.98, 1.03)</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>&gt;0.99</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>Table 5m. GLM Poisson -- Prior Hospitalizations</t>
-  </si>
-  <si>
-    <t>GLM Poisson</t>
-  </si>
-  <si>
-    <t>49369.13</t>
-  </si>
-  <si>
-    <t>49414.83</t>
-  </si>
-  <si>
-    <t>Table 5n. Panel Random-Effects Regression</t>
-  </si>
-  <si>
-    <t>Treatment exposure</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Groups</t>
-  </si>
-  <si>
-    <t>Panel RE</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>2.30</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>(0.32, 0.50)</t>
-  </si>
-  <si>
-    <t>(0.01, 0.03)</t>
-  </si>
-  <si>
-    <t>(1.70, 2.90)</t>
-  </si>
-  <si>
-    <t>Table 5o. Median Regression -- C-Reactive Protein</t>
-  </si>
-  <si>
-    <t>Median</t>
-  </si>
-  <si>
-    <t>-0.03</t>
-  </si>
-  <si>
-    <t>0.14</t>
-  </si>
-  <si>
-    <t>0.08</t>
-  </si>
-  <si>
-    <t>4.45</t>
-  </si>
-  <si>
-    <t>(-0.17, 0.10)</t>
-  </si>
-  <si>
-    <t>(-0.14, 0.13)</t>
-  </si>
-  <si>
-    <t>(0.00, 0.27)</t>
-  </si>
-  <si>
-    <t>(-0.05, 0.22)</t>
-  </si>
-  <si>
-    <t>(4.13, 4.78)</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>Table 5p. Zero-Inflated Count Models</t>
-  </si>
-  <si>
-    <t>Event count: Treatment</t>
-  </si>
-  <si>
-    <t>Event count: Age z-score</t>
-  </si>
-  <si>
-    <t>Event count: Female</t>
-  </si>
-  <si>
-    <t>Inflation equation: Female</t>
-  </si>
-  <si>
-    <t>Inflation equation: Structural-zero risk</t>
-  </si>
-  <si>
-    <t>ZIP</t>
-  </si>
-  <si>
-    <t>-0.15</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>1,500</t>
-  </si>
-  <si>
-    <t>4338.98</t>
-  </si>
-  <si>
-    <t>4376.17</t>
-  </si>
-  <si>
-    <t>-2162.49</t>
-  </si>
-  <si>
-    <t>(-0.26, -0.05)</t>
-  </si>
-  <si>
-    <t>(0.34, 0.44)</t>
-  </si>
-  <si>
-    <t>(0.19, 0.41)</t>
-  </si>
-  <si>
-    <t>(0.15, 0.84)</t>
-  </si>
-  <si>
-    <t>(0.66, 1.04)</t>
-  </si>
-  <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>ZINB</t>
-  </si>
-  <si>
-    <t>-0.14</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>1.07</t>
-  </si>
-  <si>
-    <t>4307.53</t>
-  </si>
-  <si>
-    <t>4350.04</t>
-  </si>
-  <si>
-    <t>-2145.76</t>
-  </si>
-  <si>
-    <t>(-0.26, -0.03)</t>
-  </si>
-  <si>
-    <t>(0.33, 0.45)</t>
-  </si>
-  <si>
-    <t>(0.19, 0.45)</t>
-  </si>
-  <si>
-    <t>(0.26, 1.19)</t>
-  </si>
-  <si>
-    <t>(0.79, 1.35)</t>
-  </si>
-  <si>
-    <t>0.016</t>
   </si>
   <si>
     <t>Table 5q. Cragg Hurdle Model -- Annual Cost</t>
@@ -1214,7 +1202,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="45" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B1" s="44" t="s">
         <v>1</v>
@@ -1237,7 +1225,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
@@ -1268,16 +1256,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -1285,16 +1273,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -1305,7 +1293,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D6" s="35" t="s">
         <v>1</v>
@@ -1322,7 +1310,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D7" s="31" t="s">
         <v>1</v>
@@ -1339,7 +1327,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D8" s="31" t="s">
         <v>1</v>
@@ -1356,7 +1344,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D9" s="31" t="s">
         <v>1</v>
@@ -1373,7 +1361,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D10" s="33" t="s">
         <v>1</v>
@@ -1472,7 +1460,7 @@
         <v>63</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -1489,7 +1477,7 @@
         <v>64</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -1506,7 +1494,7 @@
         <v>65</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -1523,7 +1511,7 @@
         <v>66</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
@@ -1540,7 +1528,7 @@
         <v>67</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -1557,7 +1545,7 @@
         <v>68</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -1654,7 +1642,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>1</v>
@@ -1677,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -1711,13 +1699,13 @@
         <v>46</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -1731,10 +1719,10 @@
         <v>56</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -1745,13 +1733,13 @@
         <v>48</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -1762,13 +1750,13 @@
         <v>49</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -1779,13 +1767,13 @@
         <v>50</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -1813,7 +1801,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>1</v>
@@ -1830,7 +1818,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>1</v>
@@ -1847,7 +1835,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>1</v>
@@ -1864,7 +1852,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>1</v>
@@ -1900,7 +1888,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>1</v>
@@ -1923,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -1940,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>28</v>
@@ -1963,7 +1951,7 @@
         <v>29</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5">
@@ -1977,10 +1965,10 @@
         <v>17</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -1994,10 +1982,10 @@
         <v>21</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -2011,10 +1999,10 @@
         <v>17</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8">
@@ -2022,13 +2010,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>1</v>
@@ -2039,13 +2027,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>1</v>
@@ -2076,7 +2064,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>1</v>
@@ -2093,7 +2081,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>1</v>
@@ -2110,7 +2098,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>1</v>
@@ -2163,7 +2151,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>1</v>
@@ -2186,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -2203,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>28</v>
@@ -2220,13 +2208,13 @@
         <v>46</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>119</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="5">
@@ -2243,7 +2231,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -2257,10 +2245,10 @@
         <v>17</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -2274,10 +2262,10 @@
         <v>17</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -2291,10 +2279,10 @@
         <v>17</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9">
@@ -2322,7 +2310,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>1</v>
@@ -2339,7 +2327,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>1</v>
@@ -2356,7 +2344,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>1</v>
@@ -2391,7 +2379,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>1</v>
@@ -2414,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -2431,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>28</v>
@@ -2448,13 +2436,13 @@
         <v>46</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>119</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="5">
@@ -2471,7 +2459,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -2485,10 +2473,10 @@
         <v>17</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -2502,10 +2490,10 @@
         <v>17</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -2519,10 +2507,10 @@
         <v>17</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9">
@@ -2550,7 +2538,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>1</v>
@@ -2567,7 +2555,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>1</v>
@@ -2601,7 +2589,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>1</v>
@@ -2624,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -2655,16 +2643,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>135</v>
-      </c>
       <c r="D4" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -2672,16 +2660,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="D5" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -2692,13 +2680,13 @@
         <v>51</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -2709,7 +2697,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>1</v>
@@ -2723,10 +2711,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>1</v>
@@ -2759,7 +2747,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>1</v>
@@ -2782,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -2816,13 +2804,13 @@
         <v>46</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>148</v>
-      </c>
       <c r="E4" s="10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5">
@@ -2839,7 +2827,7 @@
         <v>64</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
@@ -2850,13 +2838,13 @@
         <v>48</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>155</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -2867,13 +2855,13 @@
         <v>49</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8">
@@ -2884,13 +2872,13 @@
         <v>50</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9">
@@ -2901,13 +2889,13 @@
         <v>51</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -2971,7 +2959,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="23" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>1</v>
@@ -3003,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -3012,7 +3000,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>1</v>
@@ -3052,25 +3040,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>177</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G4" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="5">
@@ -3078,25 +3066,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -3104,25 +3092,25 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -3130,25 +3118,25 @@
         <v>1</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8">
@@ -3156,25 +3144,25 @@
         <v>1</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>40</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -3185,7 +3173,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>1</v>
@@ -3194,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>1</v>
@@ -3211,7 +3199,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>1</v>
@@ -3220,7 +3208,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>1</v>
@@ -3237,7 +3225,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>1</v>
@@ -3246,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>1</v>
@@ -3263,7 +3251,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>1</v>
@@ -3272,7 +3260,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>1</v>

--- a/tabtools/demo/demo_regtab_models.xlsx
+++ b/tabtools/demo/demo_regtab_models.xlsx
@@ -273,7 +273,7 @@
     <t>(-0.02, 0.08)</t>
   </si>
   <si>
-    <t>(-0.00, 0.00)</t>
+    <t>(0.00, 0.00)</t>
   </si>
   <si>
     <t>(-0.04, 0.05)</t>
